--- a/public/exports-60-250/29189773.xlsx
+++ b/public/exports-60-250/29189773.xlsx
@@ -6439,12 +6439,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086998</t>
+          <t xml:space="preserve">311086994</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087002</t>
+          <t xml:space="preserve">311086999</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087012</t>
+          <t xml:space="preserve">311087008</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087009</t>
+          <t xml:space="preserve">311086987</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884431</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M127" t="inlineStr">
